--- a/Phase 3 - Formal Modeling/language definition.xlsx
+++ b/Phase 3 - Formal Modeling/language definition.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Francesco\Desktop\KG project\KG-2025-26-UniTn-Project\Phase 3 - Formal Modeling\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2580F121-6867-416C-B23B-C0CED9FFBEED}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1D84280-76B2-4BC3-94CE-592409A9C01A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{253035B1-88A8-46D5-9D92-9265E858590C}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="90" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="111">
   <si>
     <t>English Word</t>
   </si>
@@ -300,6 +300,75 @@
   </si>
   <si>
     <t>https://it.wiktionary.org/wiki/indirizzo</t>
+  </si>
+  <si>
+    <t>private school</t>
+  </si>
+  <si>
+    <t>scuola paritaria/equiparata</t>
+  </si>
+  <si>
+    <t>kindergartend</t>
+  </si>
+  <si>
+    <t>asilo nido, scuola dell'infanzia</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Private_school</t>
+  </si>
+  <si>
+    <t>https://it.wikipedia.org/wiki/Scuola_privata</t>
+  </si>
+  <si>
+    <t>A school not administered or funded by the government, unlike a public school</t>
+  </si>
+  <si>
+    <t>https://it.wiktionary.org/wiki/asilo</t>
+  </si>
+  <si>
+    <t>Institution where children below school age play and are looked after during the day</t>
+  </si>
+  <si>
+    <t>https://en.wiktionary.org/wiki/Kindergarten</t>
+  </si>
+  <si>
+    <t>scuola elementare, primaria</t>
+  </si>
+  <si>
+    <t>elementary / primary school</t>
+  </si>
+  <si>
+    <t>https://en.wikipedia.org/wiki/Primary_school</t>
+  </si>
+  <si>
+    <t>https://it.wikipedia.org/wiki/Scuola_primaria</t>
+  </si>
+  <si>
+    <t>School for children of age between 6 and 11 years</t>
+  </si>
+  <si>
+    <t>https://it.wikipedia.org/wiki/Scuola_secondaria_di_primo_grado_in_Italia</t>
+  </si>
+  <si>
+    <t>scuola media / secondaria di primo grado</t>
+  </si>
+  <si>
+    <t>scuola superiore / secondaria di secondo grado</t>
+  </si>
+  <si>
+    <t>https://it.wikipedia.org/wiki/Scuola_secondaria_di_secondo_grado_in_Italia</t>
+  </si>
+  <si>
+    <t>School for children of age between 14 and 19 years</t>
+  </si>
+  <si>
+    <t>School for children of age between 12 and 13 years</t>
+  </si>
+  <si>
+    <t>middle school</t>
+  </si>
+  <si>
+    <t>high school</t>
   </si>
 </sst>
 </file>
@@ -697,7 +766,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{062DBFA5-2F75-4B4C-8B72-E0E80C5BB557}">
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F26"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="21.44140625" customWidth="1"/>
@@ -1018,6 +1087,85 @@
       </c>
       <c r="E21" s="2" t="s">
         <v>87</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A22" t="s">
+        <v>88</v>
+      </c>
+      <c r="B22" t="s">
+        <v>94</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>92</v>
+      </c>
+      <c r="D22" t="s">
+        <v>89</v>
+      </c>
+      <c r="E22" s="2" t="s">
+        <v>93</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A23" t="s">
+        <v>90</v>
+      </c>
+      <c r="B23" t="s">
+        <v>96</v>
+      </c>
+      <c r="C23" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="D23" t="s">
+        <v>91</v>
+      </c>
+      <c r="E23" s="2" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A24" t="s">
+        <v>99</v>
+      </c>
+      <c r="B24" t="s">
+        <v>102</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>100</v>
+      </c>
+      <c r="D24" t="s">
+        <v>98</v>
+      </c>
+      <c r="E24" s="2" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A25" t="s">
+        <v>109</v>
+      </c>
+      <c r="B25" t="s">
+        <v>108</v>
+      </c>
+      <c r="D25" t="s">
+        <v>104</v>
+      </c>
+      <c r="E25" s="2" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A26" t="s">
+        <v>110</v>
+      </c>
+      <c r="B26" t="s">
+        <v>107</v>
+      </c>
+      <c r="D26" t="s">
+        <v>105</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>106</v>
       </c>
     </row>
   </sheetData>
@@ -1046,6 +1194,14 @@
     <hyperlink ref="E19" r:id="rId22" xr:uid="{7EC42169-8445-4312-A15C-C010FF929A6D}"/>
     <hyperlink ref="C21" r:id="rId23" xr:uid="{54540240-FFB0-4393-8104-E6FF981D9E4C}"/>
     <hyperlink ref="E21" r:id="rId24" xr:uid="{A7D20CC4-8D5A-485F-8F96-562047E7F0E1}"/>
+    <hyperlink ref="C22" r:id="rId25" xr:uid="{8DC54A18-D1DE-41FE-BE56-20CE6B83B5EF}"/>
+    <hyperlink ref="E22" r:id="rId26" xr:uid="{A98E3DEE-567C-412B-A9FA-9684744EA7DE}"/>
+    <hyperlink ref="E23" r:id="rId27" xr:uid="{AA820276-B4FD-4F86-B52C-C3B44634A6CC}"/>
+    <hyperlink ref="C23" r:id="rId28" xr:uid="{1E013209-0EBF-488E-8650-D14D259EDD7B}"/>
+    <hyperlink ref="C24" r:id="rId29" xr:uid="{7796E31E-4DD3-4B31-8CE2-F89150933F6A}"/>
+    <hyperlink ref="E24" r:id="rId30" xr:uid="{8AAEC2DC-CA40-48BB-A2F6-8A086B346421}"/>
+    <hyperlink ref="E25" r:id="rId31" xr:uid="{2E94024D-D4E9-4670-B423-112C747C5EFD}"/>
+    <hyperlink ref="E26" r:id="rId32" xr:uid="{A8240A5F-9CB4-4E35-851E-A37D7E9EE081}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
